--- a/mes-plugins/mes-plugins-material-flow-resources/src/main/resources/materialFlowResources/public/resources/positionImportSchema_pl.xlsx
+++ b/mes-plugins/mes-plugins-material-flow-resources/src/main/resources/materialFlowResources/public/resources/positionImportSchema_pl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krna/Projects/mes/mes-plugins/mes-plugins-material-flow-resources/src/main/resources/materialFlowResources/public/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akazmierczak\Documents\Quantum Qguar\Qcadoo\Szablony\Import do Qcadoo\propozycje\PL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38EF282-ED04-ED43-826C-0F89C97FAE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C238F9C5-23B7-401E-BF32-134818E5FABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pozycje dok. przych. - import" sheetId="1" r:id="rId1"/>
@@ -49,16 +49,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana wymagana. Podaj numer produktu zdefiniowanego w qcadoo.</t>
@@ -73,16 +71,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana wymagana. Wartość musi być liczbowa i większa od 0. Jest to ilość w jednostce podstawowej produktu.</t>
@@ -97,16 +93,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana opcjonalna. Jeśli prowadzisz ewidencję produktu w dwóch jednostkach, to tu podaj ilość 
@@ -120,49 +114,46 @@
           <rPr>
             <b/>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Dana wymagana, jeśli uzupełnisz </t>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t xml:space="preserve">
+Dana wymagana, jeśli uzupełnisz </t>
         </r>
         <r>
           <rPr>
             <i/>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+            <charset val="238"/>
           </rPr>
           <t>Ilość dodatkowa</t>
         </r>
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>. Podaj jaki jest przelicznik między jednostkami. Przykład: masz jednostkę podstawową karton oraz dodatkową sztuka, a w kartonie mieści się 20 sztuk - zatem przelicznik to 20.</t>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+            <charset val="238"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t xml:space="preserve"> Podaj jaki jest przelicznik między jednostkami. Przykład: masz jednostkę podstawową karton oraz dodatkową sztuka, a w kartonie mieści się 20 sztuk - zatem przelicznik to 20.</t>
         </r>
       </text>
     </comment>
@@ -174,16 +165,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana opcjonalna. Cena 
@@ -200,16 +189,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana opcjonalna. Numer partii przyjmowanego produktu. Na tej podstawie zostanie założona partia w genealogii i odpowiednio podpięta do dokumentu.</t>
@@ -224,16 +211,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana opcjonalna. Zapisz w formacie DD.MM.RRRR</t>
@@ -248,16 +233,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana opcjonalna. Zapisz w formacie DD.MM.RRRR</t>
@@ -272,16 +255,14 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
           </rPr>
           <t xml:space="preserve">
 Dana opcjonalna. Podaj miejsce składowania zdefiniowane w qcadoo. Ważne, aby była to lokalizacja przypisana do magazynu wskazanego w nagłówku dokumentu.</t>
@@ -294,30 +275,19 @@
           <rPr>
             <b/>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dana opcjonalna. Jeśli składujesz produkty na paletach, to wskaż tu wartość zdefiniowaną w słowniku typów palet.</t>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t xml:space="preserve">
+Dana opcjonalna. Jeśli składujesz produkty na paletach, to wskaż tu wartość zdefiniowaną w słowniku typów palet.</t>
         </r>
       </text>
     </comment>
@@ -327,40 +297,20 @@
           <rPr>
             <b/>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Dana opcjonalna. Jeśli składujesz produkty na paletach, to wprowadź tutaj numer palety zdefiniowanej 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>w qcadoo.</t>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t>qcadoo MES:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
+          </rPr>
+          <t xml:space="preserve">
+Dana opcjonalna. Jeśli składujesz produkty na paletach, to wprowadź tutaj numer palety zdefiniowanej 
+w qcadoo.</t>
         </r>
       </text>
     </comment>
@@ -398,30 +348,22 @@
     <t>Miejsce składowania</t>
   </si>
   <si>
-    <t>Typ nośnika</t>
-  </si>
-  <si>
-    <t>Numer nośnika</t>
+    <t>Typ palety</t>
+  </si>
+  <si>
+    <t>Numer palety</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -454,13 +396,11 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -472,24 +412,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -512,13 +445,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -527,53 +459,53 @@
     <dxf>
       <font>
         <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
         <i/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
       </font>
     </dxf>
     <dxf>
@@ -647,16 +579,16 @@
   <autoFilter ref="A1:K2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Produkt" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Ilość" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ilość dodatkowa" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Przelicznik" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Cena" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Partia" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data produkcji" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Data ważności" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Miejsce składowania" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Typ nośnika" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Numer nośnika" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Ilość" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ilość dodatkowa" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Przelicznik" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Cena" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Partia" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data produkcji" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Data ważności" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Miejsce składowania" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Typ palety" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Numer palety" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Styl tabeli 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -929,14 +861,14 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.1640625" customWidth="1"/>
-    <col min="10" max="11" width="16.83203125" customWidth="1"/>
+    <col min="1" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="20.25" customWidth="1"/>
+    <col min="10" max="11" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -964,14 +896,14 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
